--- a/data/estad_portales/Rendimiento_p3.xlsx
+++ b/data/estad_portales/Rendimiento_p3.xlsx
@@ -427,25 +427,25 @@
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="2" t="str">
-        <v>14/08/2026</v>
+        <v>21/08/2026</v>
       </c>
       <c r="B2" s="2">
-        <v>4541</v>
+        <v>4813</v>
       </c>
       <c r="C2" s="2">
-        <v>217</v>
+        <v>313</v>
       </c>
       <c r="D2" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="str">
         <v/>
@@ -453,25 +453,25 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="2" t="str">
-        <v>15/08/2026</v>
+        <v>22/08/2026</v>
       </c>
       <c r="B3" s="2">
-        <v>4060</v>
+        <v>4366</v>
       </c>
       <c r="C3" s="2">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
         <v>6</v>
       </c>
       <c r="G3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="str">
         <v/>
@@ -479,25 +479,25 @@
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="2" t="str">
-        <v>16/08/2026</v>
+        <v>23/08/2026</v>
       </c>
       <c r="B4" s="2">
-        <v>4789</v>
+        <v>4559</v>
       </c>
       <c r="C4" s="2">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="str">
         <v/>
@@ -505,25 +505,25 @@
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="2" t="str">
-        <v>17/08/2026</v>
+        <v>24/08/2026</v>
       </c>
       <c r="B5" s="2">
-        <v>5546</v>
+        <v>5864</v>
       </c>
       <c r="C5" s="2">
-        <v>325</v>
+        <v>387</v>
       </c>
       <c r="D5" s="2">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
         <v>10</v>
       </c>
-      <c r="E5" s="2">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>8</v>
-      </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="str">
         <v/>
@@ -531,25 +531,25 @@
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="2" t="str">
-        <v>18/08/2026</v>
+        <v>25/08/2026</v>
       </c>
       <c r="B6" s="2">
-        <v>5389</v>
+        <v>6035</v>
       </c>
       <c r="C6" s="2">
-        <v>299</v>
+        <v>388</v>
       </c>
       <c r="D6" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G6" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="str">
         <v/>
@@ -557,25 +557,25 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="2" t="str">
-        <v>19/08/2026</v>
+        <v>26/08/2026</v>
       </c>
       <c r="B7" s="2">
-        <v>5314</v>
+        <v>5407</v>
       </c>
       <c r="C7" s="2">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="D7" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="str">
         <v/>
@@ -583,22 +583,22 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="2" t="str">
-        <v>20/08/2026</v>
+        <v>27/08/2026</v>
       </c>
       <c r="B8" s="2">
-        <v>5361</v>
+        <v>5293</v>
       </c>
       <c r="C8" s="2">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="D8" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>
